--- a/Reports/Lobewise Comparisons/ResultsFinal/ggo.xlsx
+++ b/Reports/Lobewise Comparisons/ResultsFinal/ggo.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="109" documentId="11_F25DC773A252ABDACC1048CA799F592E5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E583E0FB-E302-4DE9-A5BB-606FF38F2787}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO_main" sheetId="1" r:id="rId1"/>
@@ -141,9 +141,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +460,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
@@ -484,7 +483,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3">
@@ -510,7 +509,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4">
@@ -536,7 +535,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
@@ -559,7 +558,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6">
@@ -585,7 +584,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7">
@@ -608,7 +607,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
@@ -631,7 +630,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
@@ -654,7 +653,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
@@ -677,7 +676,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11">
@@ -703,7 +702,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="B12">
@@ -729,7 +728,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13">
@@ -755,7 +754,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14">
@@ -778,7 +777,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15">
@@ -801,7 +800,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>12</v>
       </c>
       <c r="B16">
@@ -860,7 +859,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
@@ -883,7 +882,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3">
@@ -909,7 +908,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
@@ -932,7 +931,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
@@ -955,7 +954,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
@@ -978,7 +977,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
@@ -1001,7 +1000,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
       <c r="B8">
@@ -1027,7 +1026,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9">
@@ -1053,7 +1052,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>20</v>
       </c>
       <c r="B10">
@@ -1079,7 +1078,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11">
@@ -1105,7 +1104,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
@@ -1128,7 +1127,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13">
@@ -1151,7 +1150,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14">
@@ -1177,7 +1176,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15">
@@ -1200,7 +1199,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16">

--- a/Reports/Lobewise Comparisons/ResultsFinal/ggo.xlsx
+++ b/Reports/Lobewise Comparisons/ResultsFinal/ggo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c2d16a148962151/Desktop/BIOSTAT/Thesis/Thesis/Reports/Lobewise Comparisons/ResultsFinal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_F25DC773A252ABDACC1048CA799F592E5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E583E0FB-E302-4DE9-A5BB-606FF38F2787}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="11_F25DC773A252ABDACC1048CA799F592E5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77016349-EA53-4117-8353-C7DFB5416287}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO_main" sheetId="1" r:id="rId1"/>
@@ -890,12 +890,12 @@
         <v>3.0270008475602372</v>
       </c>
       <c r="C3">
+        <f>1/0.60858</f>
+        <v>1.643169345032699</v>
+      </c>
+      <c r="D3">
         <f>1/0.17933</f>
         <v>5.5763118273573857</v>
-      </c>
-      <c r="D3">
-        <f>1/0.60858</f>
-        <v>1.643169345032699</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1008,12 +1008,12 @@
         <v>1.7958479994253287</v>
       </c>
       <c r="C8">
+        <f>1/1.0531</f>
+        <v>0.94957743804007222</v>
+      </c>
+      <c r="D8">
         <f>1/0.29443</f>
         <v>3.3963930306015011</v>
-      </c>
-      <c r="D8">
-        <f>1/1.0531</f>
-        <v>0.94957743804007222</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1034,12 +1034,12 @@
         <v>1.7507615812878601</v>
       </c>
       <c r="C9">
+        <f>1/1.07933</f>
+        <v>0.92650069950802827</v>
+      </c>
+      <c r="D9">
         <f>1/0.30227</f>
         <v>3.3083005260197837</v>
-      </c>
-      <c r="D9">
-        <f>1/1.07933</f>
-        <v>0.92650069950802827</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1060,12 +1060,12 @@
         <v>1.4742087184703612</v>
       </c>
       <c r="C10">
+        <f>1/1.174</f>
+        <v>0.85178875638841567</v>
+      </c>
+      <c r="D10">
         <f>1/0.39194</f>
         <v>2.5514109302444252</v>
-      </c>
-      <c r="D10">
-        <f>1/1.174</f>
-        <v>0.85178875638841567</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1086,12 +1086,12 @@
         <v>1.4576197070184387</v>
       </c>
       <c r="C11">
+        <f>1/1.32001</f>
+        <v>0.75757001840895155</v>
+      </c>
+      <c r="D11">
         <f>1/0.35656</f>
         <v>2.8045770697778778</v>
-      </c>
-      <c r="D11">
-        <f>1/1.32001</f>
-        <v>0.75757001840895155</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1158,12 +1158,12 @@
         <v>1.2320429736589211</v>
       </c>
       <c r="C14">
+        <f>1/1.49179</f>
+        <v>0.67033563705347265</v>
+      </c>
+      <c r="D14">
         <f>1/0.44161</f>
         <v>2.2644414755100652</v>
-      </c>
-      <c r="D14">
-        <f>1/1.49179</f>
-        <v>0.67033563705347265</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1207,12 +1207,12 @@
         <v>1.0257567520438202</v>
       </c>
       <c r="C16">
+        <f>1/1.91611</f>
+        <v>0.5218907056484231</v>
+      </c>
+      <c r="D16">
         <f>1/0.49601</f>
         <v>2.0160883853148124</v>
-      </c>
-      <c r="D16">
-        <f>1/1.91611</f>
-        <v>0.5218907056484231</v>
       </c>
       <c r="E16">
         <v>0</v>
